--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6C6AC6-3214-4B99-96C1-96CEA70790BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF40B13-4F5C-44B8-9D3D-7F8409C0B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2024,6 +2024,157 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457198</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>153025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>432525</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>61686</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="12" name="组合 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1537F2EE-F02E-867E-60E2-E6FC03F5E12A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5613398" y="4097282"/>
+          <a:ext cx="1956527" cy="1686661"/>
+          <a:chOff x="370113" y="871482"/>
+          <a:chExt cx="1956527" cy="1686661"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="等腰三角形 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{647846D4-DB6C-5560-FEEA-DF81FE940CE8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="370113" y="871482"/>
+            <a:ext cx="1956527" cy="1686661"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="11" name="箭头: 环形 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B064810-AB24-28A7-2C1A-10DADB50E207}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="2147707">
+            <a:off x="1632857" y="888999"/>
+            <a:ext cx="464458" cy="464458"/>
+          </a:xfrm>
+          <a:prstGeom prst="circularArrow">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 7895"/>
+              <a:gd name="adj2" fmla="val 1281339"/>
+              <a:gd name="adj3" fmla="val 20107237"/>
+              <a:gd name="adj4" fmla="val 10800000"/>
+              <a:gd name="adj5" fmla="val 12500"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF40B13-4F5C-44B8-9D3D-7F8409C0B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BB77D-6AD4-4143-9FD1-F9C43B8C3FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2175,6 +2175,228 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>506358</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>27044</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>165273</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>49160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="箭头: 右 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E4EC7CE-F3AF-D997-C03D-14ADCFB7576A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7805058" y="4826001"/>
+          <a:ext cx="1977916" cy="979715"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+            <a:gd name="adj2" fmla="val 86296"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>68943</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>79203</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>584202</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>6634</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="13" name="组合 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D11B455-099C-4303-8D56-40F2252A35AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3904343" y="6157060"/>
+          <a:ext cx="1175659" cy="1705431"/>
+          <a:chOff x="921656" y="888999"/>
+          <a:chExt cx="1175659" cy="1705431"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="等腰三角形 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10158F1A-FF85-111D-2D0B-838DBDC7477C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="921656" y="907769"/>
+            <a:ext cx="827314" cy="1686661"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="箭头: 环形 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27301D84-45D1-36E9-CA0C-775B6A21F94C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="2147707">
+            <a:off x="1632857" y="888999"/>
+            <a:ext cx="464458" cy="464458"/>
+          </a:xfrm>
+          <a:prstGeom prst="circularArrow">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 7895"/>
+              <a:gd name="adj2" fmla="val 1281339"/>
+              <a:gd name="adj3" fmla="val 20107237"/>
+              <a:gd name="adj4" fmla="val 10800000"/>
+              <a:gd name="adj5" fmla="val 12500"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BB77D-6AD4-4143-9FD1-F9C43B8C3FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1A0CF4-D452-4961-B2D0-F9069EF11C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2177,77 +2177,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>506358</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>27044</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>165273</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>49160</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="箭头: 右 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E4EC7CE-F3AF-D997-C03D-14ADCFB7576A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="7805058" y="4826001"/>
-          <a:ext cx="1977916" cy="979715"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightArrow">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 50000"/>
-            <a:gd name="adj2" fmla="val 86296"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>68943</xdr:colOff>
       <xdr:row>26</xdr:row>
@@ -2345,6 +2274,160 @@
         <xdr:spPr>
           <a:xfrm rot="2147707">
             <a:off x="1632857" y="888999"/>
+            <a:ext cx="464458" cy="464458"/>
+          </a:xfrm>
+          <a:prstGeom prst="circularArrow">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 7895"/>
+              <a:gd name="adj2" fmla="val 1281339"/>
+              <a:gd name="adj3" fmla="val 20107237"/>
+              <a:gd name="adj4" fmla="val 10800000"/>
+              <a:gd name="adj5" fmla="val 12500"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>473700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>12528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>406401</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>34644</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="17" name="组合 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A926FCB-6605-52A3-8A36-2589B94B2B8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="8271500" y="4312385"/>
+          <a:ext cx="1253501" cy="1977916"/>
+          <a:chOff x="8304158" y="4323272"/>
+          <a:chExt cx="1253501" cy="1977916"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="箭头: 右 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E4EC7CE-F3AF-D997-C03D-14ADCFB7576A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="16200000">
+            <a:off x="7805058" y="4822372"/>
+            <a:ext cx="1977916" cy="979715"/>
+          </a:xfrm>
+          <a:prstGeom prst="rightArrow">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+              <a:gd name="adj2" fmla="val 86296"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="16" name="箭头: 环形 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70BB260B-965F-4F78-A42F-45127F05C8CA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="2147707">
+            <a:off x="9093201" y="4383314"/>
             <a:ext cx="464458" cy="464458"/>
           </a:xfrm>
           <a:prstGeom prst="circularArrow">

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1A0CF4-D452-4961-B2D0-F9069EF11C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8FB1D3-47E5-465F-9080-E4262639A820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2480,6 +2480,262 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>487143</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>136561</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>287911</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>6276</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="22" name="组合 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF6AD29D-6F2D-1CF4-D805-85F9840A6D26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5643343" y="6036618"/>
+          <a:ext cx="1781968" cy="1825515"/>
+          <a:chOff x="454485" y="793333"/>
+          <a:chExt cx="1781968" cy="1825515"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="等腰三角形 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C01BC32B-DE5E-AB91-582A-CC924E7A527F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="18900000">
+            <a:off x="503099" y="793333"/>
+            <a:ext cx="523592" cy="599056"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="19" name="等腰三角形 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3275ADE4-8BAE-814B-AB8F-BAE5BAF2BC38}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="2700000">
+            <a:off x="1675129" y="800590"/>
+            <a:ext cx="523592" cy="599056"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="sysDot"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="20" name="等腰三角形 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2EC9D4-A413-8674-4667-DFD49014807C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="8100000">
+            <a:off x="1671503" y="2019792"/>
+            <a:ext cx="523592" cy="599056"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="sysDot"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="等腰三角形 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D227A2A7-1F8C-2EF0-7A35-694802D01178}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="13500000">
+            <a:off x="492217" y="2034306"/>
+            <a:ext cx="523592" cy="599056"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="sysDot"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8FB1D3-47E5-465F-9080-E4262639A820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4E5D46-F868-4026-BD09-9C000A138698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2482,258 +2482,70 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>487143</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>136561</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>195942</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>159657</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>287911</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>6276</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>119743</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>32658</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="22" name="组合 21">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="直角三角形 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF6AD29D-6F2D-1CF4-D805-85F9840A6D26}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDFCF3AB-6D32-8A1A-A2BC-D3FAB7FB301F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="5643343" y="6036618"/>
-          <a:ext cx="1781968" cy="1825515"/>
-          <a:chOff x="454485" y="793333"/>
-          <a:chExt cx="1781968" cy="1825515"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3370942" y="4281714"/>
+          <a:ext cx="584201" cy="584201"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="等腰三角形 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C01BC32B-DE5E-AB91-582A-CC924E7A527F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="18900000">
-            <a:off x="503099" y="793333"/>
-            <a:ext cx="523592" cy="599056"/>
-          </a:xfrm>
-          <a:prstGeom prst="triangle">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg2"/>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="等腰三角形 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3275ADE4-8BAE-814B-AB8F-BAE5BAF2BC38}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="2700000">
-            <a:off x="1675129" y="800590"/>
-            <a:ext cx="523592" cy="599056"/>
-          </a:xfrm>
-          <a:prstGeom prst="triangle">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="95000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:prstDash val="sysDot"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="等腰三角形 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2EC9D4-A413-8674-4667-DFD49014807C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="8100000">
-            <a:off x="1671503" y="2019792"/>
-            <a:ext cx="523592" cy="599056"/>
-          </a:xfrm>
-          <a:prstGeom prst="triangle">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="95000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:prstDash val="sysDot"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="等腰三角形 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D227A2A7-1F8C-2EF0-7A35-694802D01178}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="13500000">
-            <a:off x="492217" y="2034306"/>
-            <a:ext cx="523592" cy="599056"/>
-          </a:xfrm>
-          <a:prstGeom prst="triangle">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="95000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:prstDash val="sysDot"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rtTriangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4E5D46-F868-4026-BD09-9C000A138698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E8B874-8620-48FE-9B08-61B8E5A57D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2548,6 +2548,74 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>181431</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>68944</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>170546</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>79830</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="矩形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8A2A7CA-3233-4FF1-9BEC-EC60D9D2B373}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="18900000">
+          <a:off x="5337631" y="6858001"/>
+          <a:ext cx="1970315" cy="188686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E8B874-8620-48FE-9B08-61B8E5A57D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC86297-C5BC-4E74-9AAD-AF1E0CDDFFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2616,6 +2616,74 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>526142</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>43542</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="菱形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{259D7440-663C-9FF5-C8D8-690D9BC5A7A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7010400" y="6281057"/>
+          <a:ext cx="1973942" cy="1973942"/>
+        </a:xfrm>
+        <a:prstGeom prst="diamond">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC86297-C5BC-4E74-9AAD-AF1E0CDDFFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632FEE15-C910-458F-9047-CA5E6CF677F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -2684,6 +2684,92 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>221344</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>10891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>214087</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>112837</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="五边形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{085119E4-20A8-6804-777A-48B28313C8ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10000344" y="4666348"/>
+          <a:ext cx="1973943" cy="1879946"/>
+        </a:xfrm>
+        <a:prstGeom prst="pentagon">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="5400" b="1" i="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="MiSans Medium" pitchFamily="2" charset="-122"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>n</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="5400" b="1" i="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            <a:ea typeface="MiSans Medium" pitchFamily="2" charset="-122"/>
+            <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632FEE15-C910-458F-9047-CA5E6CF677F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79E4E6A-BE8B-43DF-878F-DB7A71ED61BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -208,6 +208,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFFF6699"/>
       <color rgb="FF9900FF"/>
     </mruColors>
   </colors>
@@ -2482,16 +2484,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>195942</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>159657</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>322942</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>148771</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>119743</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>32658</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>246743</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>21772</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2506,7 +2508,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="3370942" y="4281714"/>
+          <a:off x="9441542" y="6582228"/>
           <a:ext cx="584201" cy="584201"/>
         </a:xfrm>
         <a:prstGeom prst="rtTriangle">
@@ -2768,6 +2770,275 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>192314</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>31968</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>192430</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>61803</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="32" name="组合 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD5C42F0-4916-C02C-0290-61939370C757}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="9971314" y="6998825"/>
+          <a:ext cx="1981316" cy="1985635"/>
+          <a:chOff x="355600" y="721395"/>
+          <a:chExt cx="1981316" cy="1985635"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="矩形: 单圆角 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2460B91-E634-48CD-6B1E-C386366C785A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeAspect="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1345508" y="725713"/>
+            <a:ext cx="991408" cy="990000"/>
+          </a:xfrm>
+          <a:prstGeom prst="round1Rect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 35266"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFCCCC"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="26" name="矩形: 单圆角 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF08806-42E4-48BA-8EDD-7964511C1208}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeAspect="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="1344261" y="1716326"/>
+            <a:ext cx="991408" cy="990000"/>
+          </a:xfrm>
+          <a:prstGeom prst="round1Rect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 35266"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="27" name="矩形: 单圆角 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3979134-9430-47D1-94A3-DDF4C3A0C540}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeAspect="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="10800000">
+            <a:off x="355600" y="1716314"/>
+            <a:ext cx="991408" cy="990000"/>
+          </a:xfrm>
+          <a:prstGeom prst="round1Rect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 35266"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFCCCC"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="28" name="矩形: 单圆角 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07DAD953-CF2A-4442-AD21-5BF929551B64}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeAspect="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="16200000">
+            <a:off x="357982" y="722099"/>
+            <a:ext cx="991408" cy="990000"/>
+          </a:xfrm>
+          <a:prstGeom prst="round1Rect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 35266"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79E4E6A-BE8B-43DF-878F-DB7A71ED61BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128E065-3A0F-434B-8228-C9E931B34DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -3041,6 +3041,435 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>573320</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>54427</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>156036</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>83453</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="46" name="组合 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF0084DE-CB2E-F298-B564-36DB3258B70B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2249720" y="5954484"/>
+          <a:ext cx="1081316" cy="1984826"/>
+          <a:chOff x="787407" y="725713"/>
+          <a:chExt cx="1081316" cy="1984826"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="六边形 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51CB00FA-EE09-4B45-53D9-94626A8B82F4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="878121" y="725713"/>
+            <a:ext cx="900000" cy="174172"/>
+          </a:xfrm>
+          <a:prstGeom prst="hexagon">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 54167"/>
+              <a:gd name="vf" fmla="val 115470"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="29" name="六边形 28">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4957EA5-8141-435C-BBA0-C6F3C2EE5A66}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="424493" y="1179341"/>
+            <a:ext cx="900000" cy="174172"/>
+          </a:xfrm>
+          <a:prstGeom prst="hexagon">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 45833"/>
+              <a:gd name="vf" fmla="val 115470"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="30" name="六边形 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED04C0BC-E764-265C-A738-60D7F19EEAB4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="878119" y="1629223"/>
+            <a:ext cx="900000" cy="174172"/>
+          </a:xfrm>
+          <a:prstGeom prst="hexagon">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 54167"/>
+              <a:gd name="vf" fmla="val 115470"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="31" name="六边形 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15692164-34B3-4AB9-25D4-3F56F11DCA97}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="1331637" y="1179340"/>
+            <a:ext cx="900000" cy="174172"/>
+          </a:xfrm>
+          <a:prstGeom prst="hexagon">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 45833"/>
+              <a:gd name="vf" fmla="val 115470"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="dash"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="33" name="六边形 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E68F458-5204-46E0-8EE6-BCE591DF6E6B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="424495" y="2079224"/>
+            <a:ext cx="900000" cy="174172"/>
+          </a:xfrm>
+          <a:prstGeom prst="hexagon">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 45833"/>
+              <a:gd name="vf" fmla="val 115470"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="dash"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="44" name="六边形 43">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8791FC8F-8FD7-42EC-B250-93283EF1215F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="1331636" y="2082855"/>
+            <a:ext cx="900000" cy="174172"/>
+          </a:xfrm>
+          <a:prstGeom prst="hexagon">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 45833"/>
+              <a:gd name="vf" fmla="val 115470"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="45" name="六边形 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED1AEC12-056A-434F-BFEE-21938601E7F0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="878121" y="2536367"/>
+            <a:ext cx="900000" cy="174172"/>
+          </a:xfrm>
+          <a:prstGeom prst="hexagon">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 54167"/>
+              <a:gd name="vf" fmla="val 115470"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128E065-3A0F-434B-8228-C9E931B34DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDA99EF-72AF-4855-8EEF-6CA07F436C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -3470,6 +3470,310 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>573317</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>58056</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>391889</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="50" name="组合 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D528ECB4-EB50-5049-7D6B-49EEBE194CD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="928917" y="3646713"/>
+          <a:ext cx="1977572" cy="1973943"/>
+          <a:chOff x="359229" y="722086"/>
+          <a:chExt cx="1977572" cy="1973943"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="22" name="等腰三角形 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{377476A1-ACEA-836E-8290-462E9E60168A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="10800000">
+            <a:off x="896257" y="722086"/>
+            <a:ext cx="910772" cy="453571"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="25" name="等腰三角形 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A0ED44B-93D9-48CB-A34A-F2081A7F2F48}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="130629" y="1509491"/>
+            <a:ext cx="910772" cy="453571"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="48" name="等腰三角形 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59AF2F1C-CDC8-4747-8913-778995A886D5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="885372" y="2242458"/>
+            <a:ext cx="910772" cy="453571"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="49" name="等腰三角形 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58A79797-DFFC-4CEB-B458-0EA13931EC37}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="16200000">
+            <a:off x="1654630" y="1487719"/>
+            <a:ext cx="910772" cy="453571"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>90714</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>315685</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>159657</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>315685</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="直接箭头连接符 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F87D1646-AF8A-2024-DB92-0415EC3C0EFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3265714" y="1694542"/>
+          <a:ext cx="1389743" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDA99EF-72AF-4855-8EEF-6CA07F436C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92313145-5369-4FA0-8E7E-2AA858097346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -166,7 +166,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -198,6 +198,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4093,6 +4096,7 @@
     </row>
     <row r="6" spans="3:5" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="6"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="3:5" ht="52" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92313145-5369-4FA0-8E7E-2AA858097346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7E028F-41AA-4674-9413-188AA797CE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -3777,6 +3777,121 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>181429</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>87086</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>522515</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>36288</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="81" name="组合 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6104C2B-52CA-1F3D-D7FF-9391204BF969}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3356429" y="3853543"/>
+          <a:ext cx="1001486" cy="1016002"/>
+          <a:chOff x="1331686" y="718457"/>
+          <a:chExt cx="1001486" cy="1016002"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="74" name="直接连接符 73">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9165FFCC-C480-BF96-2FA1-82FB3E386C06}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1331686" y="718457"/>
+            <a:ext cx="0" cy="1008743"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="57150">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="78" name="直接连接符 77">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{980B6A4D-4BC5-45BB-A40D-E9CC1EBE40E2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="1338943" y="1734459"/>
+            <a:ext cx="994229" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="57150">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Code\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7E028F-41AA-4674-9413-188AA797CE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A771AFF-6D73-477F-929F-494D729C7249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -198,9 +198,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3892,6 +3889,88 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>107095</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1431995" cy="2566215"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="文本框 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3413A2A8-6D5C-8922-57ED-0C2FC78F746C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="462695" y="5653315"/>
+          <a:ext cx="1431995" cy="2566215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="16600" b="1">
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:latin typeface="Cascadia Code" panose="020B0609020000020004" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Cascadia Code" panose="020B0609020000020004" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>!</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="16600" b="1">
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Cascadia Code" panose="020B0609020000020004" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Cascadia Code" panose="020B0609020000020004" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4211,7 +4290,6 @@
     </row>
     <row r="6" spans="3:5" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="6"/>
-      <c r="D6" s="11"/>
       <c r="E6" s="7"/>
     </row>
     <row r="7" spans="3:5" ht="52" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Code\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A771AFF-6D73-477F-929F-494D729C7249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3445D6EE-3432-4038-B381-B25E8959DAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -3971,6 +3971,74 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>163287</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>156030</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="心形 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94B5FC71-01D8-D9DA-F1CA-2B9B92A31850}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7300687" y="8498114"/>
+          <a:ext cx="1973943" cy="1973943"/>
+        </a:xfrm>
+        <a:prstGeom prst="heart">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Code\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3445D6EE-3432-4038-B381-B25E8959DAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E449A54-2741-4796-AA34-9F1BE41A525A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4039,6 +4039,65 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>156028</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>224971</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="直接箭头连接符 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F74C018-E020-4FC1-889C-09C45D201B5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5312228" y="8487228"/>
+          <a:ext cx="1389743" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="76200" cap="rnd" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Code\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E449A54-2741-4796-AA34-9F1BE41A525A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572F1290-0F23-4F97-BF75-104C6BE76B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4098,6 +4098,204 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>551543</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>72571</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>540658</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>12966</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="75" name="组合 74">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C55132F4-DF22-BC49-97E8-F3F12EA19C81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3066143" y="7928428"/>
+          <a:ext cx="1970315" cy="2073995"/>
+          <a:chOff x="359228" y="500742"/>
+          <a:chExt cx="1970315" cy="2073995"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="70" name="矩形 69">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F13C4AA7-C13D-466B-87BD-764F79F1EA9B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="18900000">
+            <a:off x="359228" y="1632857"/>
+            <a:ext cx="1970315" cy="188686"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="72" name="文本框 71">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CCB4F3C-C3BA-A14D-5916-5AD9D84B5311}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="558800" y="500742"/>
+            <a:ext cx="697627" cy="1272080"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="8000" b="1" i="1">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>x</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="8000" b="1" i="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="73" name="文本框 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870C2724-18B9-FA04-7C7F-5E310240B83D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1469570" y="1302657"/>
+            <a:ext cx="640047" cy="1272080"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN" sz="8000" b="1" i="1">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>y</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="8000" b="1" i="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Code\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572F1290-0F23-4F97-BF75-104C6BE76B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D1E509-3298-49E3-B474-390E030D6DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4296,6 +4296,76 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>453571</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>159657</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304801</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>9337</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="76" name="文本框 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D53E486-D96F-434D-BE24-B289F7622BA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1469571" y="8015514"/>
+          <a:ext cx="1349830" cy="1272080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="8000" b="0" i="0">
+              <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>VX</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="8000" b="0" i="0">
+            <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D1E509-3298-49E3-B474-390E030D6DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB5A79C-CB6E-4F13-9C32-BAC0A46BA99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4366,6 +4366,76 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>25397</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>90715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>526140</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>118195</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="文本框 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5C09A6C-0993-46F6-87E8-1567AA3DC150}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="203197" y="5101772"/>
+          <a:ext cx="678543" cy="1272080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="8000" b="0" i="0">
+              <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>7</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="8000" b="0" i="0">
+            <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB5A79C-CB6E-4F13-9C32-BAC0A46BA99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E4BF05-06B8-4BBD-9229-9602BA3458A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4436,6 +4436,76 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>195943</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>322943</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>214086</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>96423</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="79" name="文本框 78">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0034129F-3BBC-4A8D-B356-0149F46896C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4691743" y="1701800"/>
+          <a:ext cx="678543" cy="1272080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="8000" b="0" i="0">
+              <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>&gt;</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="8000" b="0" i="0">
+            <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E4BF05-06B8-4BBD-9229-9602BA3458A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22608A15-3CB7-4377-BB67-34A91A2AEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4506,6 +4506,76 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>83459</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>47170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>645887</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>74650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="80" name="文本框 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{604FCE7D-C8D9-472C-9A56-7BB8AEEA0BDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="439059" y="9325427"/>
+          <a:ext cx="1883228" cy="1272080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="8000" b="0" i="0">
+              <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>"s"</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="8000" b="0" i="0">
+            <a:latin typeface="Consolas" panose="020B0609020204030204" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22608A15-3CB7-4377-BB67-34A91A2AEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E104F20-DF6E-40BD-B057-1FD600EC4E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4576,6 +4576,231 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>166915</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>591455</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>87086</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="90" name="组合 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B20874CD-24B6-411C-9915-CA06AC45F951}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5105400" y="9267372"/>
+          <a:ext cx="1963055" cy="631371"/>
+          <a:chOff x="366487" y="1393375"/>
+          <a:chExt cx="1963055" cy="631371"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="91" name="椭圆 90">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{424713E4-04E9-F90D-612E-78BCFA8D6975}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="366487" y="1393375"/>
+            <a:ext cx="631371" cy="631371"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="92" name="椭圆 91">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAD31B9E-09F2-6697-0646-9064AE0653A4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1698171" y="1393375"/>
+            <a:ext cx="631371" cy="631371"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="93" name="直接箭头连接符 92">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08A2B74D-13DF-9262-F493-9A802AA1EAEE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="986971" y="1643745"/>
+            <a:ext cx="718457" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:tailEnd type="none"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="94" name="直接箭头连接符 93">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3D99108-A05D-A786-6F48-1462B8090816}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="986971" y="1770742"/>
+            <a:ext cx="718457" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:tailEnd type="none"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E104F20-DF6E-40BD-B057-1FD600EC4E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD4E99A-F004-4232-A483-0E1F4DAEB73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4801,6 +4801,74 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>145145</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333831</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>14516</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="83" name="矩形 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79DA83FD-E100-4040-8F78-82E56ADC959C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="-390070" y="8213273"/>
+          <a:ext cx="1970315" cy="188686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD4E99A-F004-4232-A483-0E1F4DAEB73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0012B8ED-EBD6-447E-B4A0-FD4986D366FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -4869,6 +4869,431 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>239485</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>3629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>54542</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>29142</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="86" name="组合 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6E365E2-592A-4895-9317-8C5F8A851F4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="595085" y="10526486"/>
+          <a:ext cx="1974057" cy="1981313"/>
+          <a:chOff x="362857" y="718457"/>
+          <a:chExt cx="1974057" cy="1981313"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="87" name="椭圆 86">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED2468DA-BA04-E7AD-609F-5BB3A6153DA0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="362857" y="718457"/>
+            <a:ext cx="900000" cy="900000"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="88" name="椭圆 87">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9792A363-2FB6-75F7-A0B8-96E23259B40C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1436914" y="1799770"/>
+            <a:ext cx="900000" cy="900000"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>410028</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>170543</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>406515</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>25515</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="97" name="组合 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1E99B16-D4D5-48BB-8C68-76BE0C27AC67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2924628" y="10515600"/>
+          <a:ext cx="1977687" cy="1988572"/>
+          <a:chOff x="355600" y="711200"/>
+          <a:chExt cx="1977687" cy="1988572"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="98" name="矩形 97">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AA641CC-2AE5-4CC6-2A22-85BD40019B94}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="355600" y="711200"/>
+            <a:ext cx="900000" cy="900000"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="99" name="矩形 98">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29BA29AB-DD8C-ABD6-CEC9-9881CE4F332B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1433287" y="1799772"/>
+            <a:ext cx="900000" cy="900000"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>359229</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>3628</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>373016</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>32657</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="103" name="组合 102">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3129B42C-6141-4CA1-AD09-16B7686BC332}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5515429" y="10526485"/>
+          <a:ext cx="1994987" cy="1984829"/>
+          <a:chOff x="351971" y="714829"/>
+          <a:chExt cx="1994987" cy="1984829"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="104" name="等腰三角形 103">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4869FA03-4093-6CA3-6FFC-43BF88FC2F15}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="351971" y="714829"/>
+            <a:ext cx="968102" cy="834571"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="105" name="等腰三角形 104">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B556F6E-8C36-465F-3D90-8D14FF52E93C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1378856" y="1865087"/>
+            <a:ext cx="968102" cy="834571"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="38100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0012B8ED-EBD6-447E-B4A0-FD4986D366FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61E887F-8971-49F3-8FCB-B91BBF3CDCD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -5294,6 +5294,61 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>283029</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>47172</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>10885</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="89" name="直接连接符 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31DBE6C6-5773-4310-A43E-322731238ED3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7420429" y="10889342"/>
+          <a:ext cx="1745343" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="76200">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
+++ b/src/Sudoku.Graphics.UI/Assets/Unused/Icons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\source\repos\Sudoku.Graphics\src\Sudoku.Graphics.UI\Assets\Unused\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61E887F-8971-49F3-8FCB-B91BBF3CDCD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD88538-A37E-4FA3-9E9A-4401C096D9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{298DA60D-454B-478D-B88C-D8BE946E1239}"/>
   </bookViews>
@@ -5349,6 +5349,196 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>39914</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>609601</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>140606</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="107" name="组合 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB623897-49E7-4AAA-8999-D3729FD2F741}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10051143" y="9851571"/>
+          <a:ext cx="1658258" cy="456292"/>
+          <a:chOff x="478973" y="1630137"/>
+          <a:chExt cx="1658258" cy="456292"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="108" name="矩形: 圆角 107">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2799AC45-A34C-D20E-E769-22524A973C42}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="478973" y="1636486"/>
+            <a:ext cx="449943" cy="449943"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 19893"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="109" name="矩形: 圆角 108">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F001232-EAF0-5A90-7BF3-C614550C2805}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1687288" y="1636486"/>
+            <a:ext cx="449943" cy="449943"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 19893"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="110" name="直接连接符 94">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B800369-C891-D0AE-7EB9-B27A04B39624}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="108" idx="0"/>
+            <a:endCxn id="109" idx="0"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000" flipH="1" flipV="1">
+            <a:off x="1308102" y="1032329"/>
+            <a:ext cx="12700" cy="1208315"/>
+          </a:xfrm>
+          <a:prstGeom prst="bentConnector3">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 2514283"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:ln w="12700">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
